--- a/hira_material_automation/output/monthly/202601_202608__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T22:17:09</t>
+          <t>2026-08-14T21:29:11</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2fd50f7ea4017c08738184729c0af7fe7a761eed2417f03967bd8f2f5b690d9b</t>
+          <t>3507ee4b051ef029e9a635e96a0e85f0bb38eab9e7e7e19b9b7b46defbe66bd7</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202608__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T21:29:11</t>
+          <t>2026-08-24T21:34:18</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3507ee4b051ef029e9a635e96a0e85f0bb38eab9e7e7e19b9b7b46defbe66bd7</t>
+          <t>563b4e732f9e9bb09fdb48234fcac75a7fbe709c60fcbca26ad129223dc1b814</t>
         </is>
       </c>
     </row>
